--- a/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_fewshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_fewshot_cot.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -17629,7 +17629,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20536,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21097,7 +21097,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21760,7 +21760,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -22627,7 +22627,7 @@
       </c>
       <c r="C1306" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23477,7 +23477,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23596,7 @@
       </c>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8</v>
+        <v>0.7956834532374101</v>
       </c>
     </row>
     <row r="3">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7237069443063398</v>
+        <v>0.7132152661983017</v>
       </c>
     </row>
     <row r="4">
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.795434125030569</v>
+        <v>0.7888246340642271</v>
       </c>
     </row>
     <row r="5">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7841168451254397</v>
+        <v>0.8032055528379058</v>
       </c>
     </row>
     <row r="6">
@@ -24149,7 +24149,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7129432190086267</v>
+        <v>0.7000240335900999</v>
       </c>
     </row>
     <row r="7">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>319.2105569899995</v>
+        <v>732.6252415500057</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2296478827266184</v>
+        <v>0.5270685191007235</v>
       </c>
     </row>
   </sheetData>
